--- a/data/nzd0394/nzd0394.xlsx
+++ b/data/nzd0394/nzd0394.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I422"/>
+  <dimension ref="A1:I423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14350,6 +14350,39 @@
       <c r="I422" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>360.1</v>
+      </c>
+      <c r="C423" t="n">
+        <v>349.13</v>
+      </c>
+      <c r="D423" t="n">
+        <v>346.71</v>
+      </c>
+      <c r="E423" t="n">
+        <v>336.41</v>
+      </c>
+      <c r="F423" t="n">
+        <v>331.27</v>
+      </c>
+      <c r="G423" t="n">
+        <v>347.65</v>
+      </c>
+      <c r="H423" t="n">
+        <v>365.41</v>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -14364,7 +14397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B430"/>
+  <dimension ref="A1:B431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18667,6 +18700,16 @@
       </c>
       <c r="B430" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>0.17</v>
       </c>
     </row>
   </sheetData>
@@ -18835,28 +18878,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>1.352320567892752</v>
+        <v>1.351192966660102</v>
       </c>
       <c r="J2" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K2" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5296354885768335</v>
+        <v>0.530396630577167</v>
       </c>
       <c r="M2" t="n">
-        <v>7.896339460039818</v>
+        <v>7.883645895290614</v>
       </c>
       <c r="N2" t="n">
-        <v>93.95825025760486</v>
+        <v>93.74960019488901</v>
       </c>
       <c r="O2" t="n">
-        <v>9.69320639714253</v>
+        <v>9.682437719649377</v>
       </c>
       <c r="P2" t="n">
-        <v>326.8984557170949</v>
+        <v>326.9099610576706</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18913,28 +18956,28 @@
         <v>0.1522</v>
       </c>
       <c r="I3" t="n">
-        <v>1.67444758619569</v>
+        <v>1.673297398201585</v>
       </c>
       <c r="J3" t="n">
+        <v>422</v>
+      </c>
+      <c r="K3" t="n">
         <v>421</v>
       </c>
-      <c r="K3" t="n">
-        <v>420</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.678320045053541</v>
+        <v>0.6790376562890335</v>
       </c>
       <c r="M3" t="n">
-        <v>7.320530467168721</v>
+        <v>7.311592447461117</v>
       </c>
       <c r="N3" t="n">
-        <v>77.49405308712285</v>
+        <v>77.32581570203274</v>
       </c>
       <c r="O3" t="n">
-        <v>8.803070662395188</v>
+        <v>8.793509862508413</v>
       </c>
       <c r="P3" t="n">
-        <v>307.491083452599</v>
+        <v>307.5027522150902</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18991,28 +19034,28 @@
         <v>0.1076</v>
       </c>
       <c r="I4" t="n">
-        <v>1.587930668066653</v>
+        <v>1.585919634193827</v>
       </c>
       <c r="J4" t="n">
+        <v>422</v>
+      </c>
+      <c r="K4" t="n">
         <v>421</v>
       </c>
-      <c r="K4" t="n">
-        <v>420</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6682018075041989</v>
+        <v>0.668572081903458</v>
       </c>
       <c r="M4" t="n">
-        <v>6.830513847198272</v>
+        <v>6.829809617687516</v>
       </c>
       <c r="N4" t="n">
-        <v>72.97352994457485</v>
+        <v>72.84860131421787</v>
       </c>
       <c r="O4" t="n">
-        <v>8.542454562043327</v>
+        <v>8.535139208836483</v>
       </c>
       <c r="P4" t="n">
-        <v>309.2935843213703</v>
+        <v>309.3139864441051</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19069,28 +19112,28 @@
         <v>0.1482</v>
       </c>
       <c r="I5" t="n">
-        <v>1.189423415716978</v>
+        <v>1.187306609408632</v>
       </c>
       <c r="J5" t="n">
+        <v>422</v>
+      </c>
+      <c r="K5" t="n">
         <v>421</v>
       </c>
-      <c r="K5" t="n">
-        <v>420</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6806326560420556</v>
+        <v>0.680614974196067</v>
       </c>
       <c r="M5" t="n">
-        <v>4.893093925731205</v>
+        <v>4.897112101708259</v>
       </c>
       <c r="N5" t="n">
-        <v>38.68891982029822</v>
+        <v>38.6506530652267</v>
       </c>
       <c r="O5" t="n">
-        <v>6.220041786057247</v>
+        <v>6.216964940003016</v>
       </c>
       <c r="P5" t="n">
-        <v>309.7616952390038</v>
+        <v>309.7831704327796</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19147,28 +19190,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1.033146784026344</v>
+        <v>1.031066288158564</v>
       </c>
       <c r="J6" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K6" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6653893876822348</v>
+        <v>0.6652111295524321</v>
       </c>
       <c r="M6" t="n">
-        <v>4.429012938879067</v>
+        <v>4.432639024614451</v>
       </c>
       <c r="N6" t="n">
-        <v>31.05317716798719</v>
+        <v>31.03050937062318</v>
       </c>
       <c r="O6" t="n">
-        <v>5.572537767300208</v>
+        <v>5.570503511409285</v>
       </c>
       <c r="P6" t="n">
-        <v>308.634657041139</v>
+        <v>308.6558851249969</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19225,28 +19268,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7980193064815241</v>
+        <v>0.7976047829823587</v>
       </c>
       <c r="J7" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K7" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07081206654242433</v>
+        <v>0.07106328633805459</v>
       </c>
       <c r="M7" t="n">
-        <v>9.746588950596545</v>
+        <v>9.727797323747362</v>
       </c>
       <c r="N7" t="n">
-        <v>490.6161027944414</v>
+        <v>489.4555833291415</v>
       </c>
       <c r="O7" t="n">
-        <v>22.14985559308325</v>
+        <v>22.12364308447281</v>
       </c>
       <c r="P7" t="n">
-        <v>327.5080832837641</v>
+        <v>327.5122646343212</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19303,28 +19346,28 @@
         <v>0.0565</v>
       </c>
       <c r="I8" t="n">
-        <v>1.929027232917656</v>
+        <v>1.928139828085445</v>
       </c>
       <c r="J8" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K8" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6750335152602368</v>
+        <v>0.6758827747960927</v>
       </c>
       <c r="M8" t="n">
-        <v>8.055061836368095</v>
+        <v>8.042421961481015</v>
       </c>
       <c r="N8" t="n">
-        <v>103.6353929103663</v>
+        <v>103.3979693428005</v>
       </c>
       <c r="O8" t="n">
-        <v>10.18014699846551</v>
+        <v>10.16847920501392</v>
       </c>
       <c r="P8" t="n">
-        <v>316.4427449341187</v>
+        <v>316.4517994602468</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19362,7 +19405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I422"/>
+  <dimension ref="A1:I423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39163,6 +39206,53 @@
         </is>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>-42.477476699531906,173.5319768638394</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>-42.47786998537243,173.5312411869862</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>-42.47831802640531,173.53057843894</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>-42.4787384482046,173.5298605585202</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>-42.47927851549319,173.52929797736235</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>-42.47993014764115,173.529066485294</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-42.48060738258897,173.52915632314944</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0394/nzd0394.xlsx
+++ b/data/nzd0394/nzd0394.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I423"/>
+  <dimension ref="A1:I424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14383,6 +14383,39 @@
       <c r="I423" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:30+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>363</v>
+      </c>
+      <c r="C424" t="n">
+        <v>351.02</v>
+      </c>
+      <c r="D424" t="n">
+        <v>349.06</v>
+      </c>
+      <c r="E424" t="n">
+        <v>339.1</v>
+      </c>
+      <c r="F424" t="n">
+        <v>332.75</v>
+      </c>
+      <c r="G424" t="n">
+        <v>349.55</v>
+      </c>
+      <c r="H424" t="n">
+        <v>368.49</v>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -14397,7 +14430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B431"/>
+  <dimension ref="A1:B432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18710,6 +18743,16 @@
       </c>
       <c r="B431" t="n">
         <v>0.17</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>0.53</v>
       </c>
     </row>
   </sheetData>
@@ -18878,28 +18921,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>1.351192966660102</v>
+        <v>1.351357924445171</v>
       </c>
       <c r="J2" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K2" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L2" t="n">
-        <v>0.530396630577167</v>
+        <v>0.5316662032199202</v>
       </c>
       <c r="M2" t="n">
-        <v>7.883645895290614</v>
+        <v>7.865780063838085</v>
       </c>
       <c r="N2" t="n">
-        <v>93.74960019488901</v>
+        <v>93.52724198221219</v>
       </c>
       <c r="O2" t="n">
-        <v>9.682437719649377</v>
+        <v>9.670948349681751</v>
       </c>
       <c r="P2" t="n">
-        <v>326.9099610576706</v>
+        <v>326.9082761650761</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18956,28 +18999,28 @@
         <v>0.1522</v>
       </c>
       <c r="I3" t="n">
-        <v>1.673297398201585</v>
+        <v>1.672978355622617</v>
       </c>
       <c r="J3" t="n">
+        <v>423</v>
+      </c>
+      <c r="K3" t="n">
         <v>422</v>
       </c>
-      <c r="K3" t="n">
-        <v>421</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.6790376562890335</v>
+        <v>0.6800057123089689</v>
       </c>
       <c r="M3" t="n">
-        <v>7.311592447461117</v>
+        <v>7.296600747057544</v>
       </c>
       <c r="N3" t="n">
-        <v>77.32581570203274</v>
+        <v>77.14380734735394</v>
       </c>
       <c r="O3" t="n">
-        <v>8.793509862508413</v>
+        <v>8.783154749140763</v>
       </c>
       <c r="P3" t="n">
-        <v>307.5027522150902</v>
+        <v>307.5059923493117</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19034,28 +19077,28 @@
         <v>0.1076</v>
       </c>
       <c r="I4" t="n">
-        <v>1.585919634193827</v>
+        <v>1.584955351015733</v>
       </c>
       <c r="J4" t="n">
+        <v>423</v>
+      </c>
+      <c r="K4" t="n">
         <v>422</v>
       </c>
-      <c r="K4" t="n">
-        <v>421</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.668572081903458</v>
+        <v>0.6693409195960194</v>
       </c>
       <c r="M4" t="n">
-        <v>6.829809617687516</v>
+        <v>6.82103707428189</v>
       </c>
       <c r="N4" t="n">
-        <v>72.84860131421787</v>
+        <v>72.68719376550882</v>
       </c>
       <c r="O4" t="n">
-        <v>8.535139208836483</v>
+        <v>8.525678492971032</v>
       </c>
       <c r="P4" t="n">
-        <v>309.3139864441051</v>
+        <v>309.3237795160349</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19112,28 +19155,28 @@
         <v>0.1482</v>
       </c>
       <c r="I5" t="n">
-        <v>1.187306609408632</v>
+        <v>1.186393813534313</v>
       </c>
       <c r="J5" t="n">
+        <v>423</v>
+      </c>
+      <c r="K5" t="n">
         <v>422</v>
       </c>
-      <c r="K5" t="n">
-        <v>421</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.680614974196067</v>
+        <v>0.6812762428673442</v>
       </c>
       <c r="M5" t="n">
-        <v>4.897112101708259</v>
+        <v>4.892260331166051</v>
       </c>
       <c r="N5" t="n">
-        <v>38.6506530652267</v>
+        <v>38.56911718165947</v>
       </c>
       <c r="O5" t="n">
-        <v>6.216964940003016</v>
+        <v>6.210403946738044</v>
       </c>
       <c r="P5" t="n">
-        <v>309.7831704327796</v>
+        <v>309.7924406096918</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19190,28 +19233,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1.031066288158564</v>
+        <v>1.029662255152925</v>
       </c>
       <c r="J6" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K6" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6652111295524321</v>
+        <v>0.6655165767361969</v>
       </c>
       <c r="M6" t="n">
-        <v>4.432639024614451</v>
+        <v>4.431633873465185</v>
       </c>
       <c r="N6" t="n">
-        <v>31.03050937062318</v>
+        <v>30.98034178884255</v>
       </c>
       <c r="O6" t="n">
-        <v>5.570503511409285</v>
+        <v>5.565998723395698</v>
       </c>
       <c r="P6" t="n">
-        <v>308.6558851249969</v>
+        <v>308.670226035386</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19268,28 +19311,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7976047829823587</v>
+        <v>0.7980204261434362</v>
       </c>
       <c r="J7" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K7" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07106328633805459</v>
+        <v>0.07145148362277642</v>
       </c>
       <c r="M7" t="n">
-        <v>9.727797323747362</v>
+        <v>9.704945160339857</v>
       </c>
       <c r="N7" t="n">
-        <v>489.4555833291415</v>
+        <v>488.3005840157423</v>
       </c>
       <c r="O7" t="n">
-        <v>22.12364308447281</v>
+        <v>22.09752438658553</v>
       </c>
       <c r="P7" t="n">
-        <v>327.5122646343212</v>
+        <v>327.5080675338922</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19346,28 +19389,28 @@
         <v>0.0565</v>
       </c>
       <c r="I8" t="n">
-        <v>1.928139828085445</v>
+        <v>1.928612425569599</v>
       </c>
       <c r="J8" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K8" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6758827747960927</v>
+        <v>0.6770474483702547</v>
       </c>
       <c r="M8" t="n">
-        <v>8.042421961481015</v>
+        <v>8.024866339402374</v>
       </c>
       <c r="N8" t="n">
-        <v>103.3979693428005</v>
+        <v>103.1550354339014</v>
       </c>
       <c r="O8" t="n">
-        <v>10.16847920501392</v>
+        <v>10.15652674066786</v>
       </c>
       <c r="P8" t="n">
-        <v>316.4517994602468</v>
+        <v>316.4469723100707</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19405,7 +19448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I423"/>
+  <dimension ref="A1:I424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39253,6 +39296,53 @@
         </is>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:30+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>-42.477495272013044,173.53200166811231</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>-42.477882089580895,173.5312573525296</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>-42.47833282284228,173.53059888005313</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>-42.47875347454984,173.5298862288672</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>-42.479285207282906,173.52931354938775</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>-42.47993520516634,173.52908856842063</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-42.480611078987614,173.52919346150085</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0394/nzd0394.xlsx
+++ b/data/nzd0394/nzd0394.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I424"/>
+  <dimension ref="A1:I425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14416,6 +14416,39 @@
       <c r="I424" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>363.17</v>
+      </c>
+      <c r="C425" t="n">
+        <v>351.41</v>
+      </c>
+      <c r="D425" t="n">
+        <v>348.91</v>
+      </c>
+      <c r="E425" t="n">
+        <v>338.3</v>
+      </c>
+      <c r="F425" t="n">
+        <v>332.88</v>
+      </c>
+      <c r="G425" t="n">
+        <v>349.18</v>
+      </c>
+      <c r="H425" t="n">
+        <v>366.52</v>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -14430,7 +14463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B432"/>
+  <dimension ref="A1:B433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18753,6 +18786,16 @@
       </c>
       <c r="B432" t="n">
         <v>0.53</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>-0.35</v>
       </c>
     </row>
   </sheetData>
@@ -18921,28 +18964,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>1.351357924445171</v>
+        <v>1.351479149865364</v>
       </c>
       <c r="J2" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K2" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5316662032199202</v>
+        <v>0.5329518114025387</v>
       </c>
       <c r="M2" t="n">
-        <v>7.865780063838085</v>
+        <v>7.847760580978392</v>
       </c>
       <c r="N2" t="n">
-        <v>93.52724198221219</v>
+        <v>93.30578481504209</v>
       </c>
       <c r="O2" t="n">
-        <v>9.670948349681751</v>
+        <v>9.659491954292529</v>
       </c>
       <c r="P2" t="n">
-        <v>326.9082761650761</v>
+        <v>326.9070264252925</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18999,28 +19042,28 @@
         <v>0.1522</v>
       </c>
       <c r="I3" t="n">
-        <v>1.672978355622617</v>
+        <v>1.672688584890807</v>
       </c>
       <c r="J3" t="n">
+        <v>424</v>
+      </c>
+      <c r="K3" t="n">
         <v>423</v>
       </c>
-      <c r="K3" t="n">
-        <v>422</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.6800057123089689</v>
+        <v>0.6810083505470863</v>
       </c>
       <c r="M3" t="n">
-        <v>7.296600747057544</v>
+        <v>7.281433260599537</v>
       </c>
       <c r="N3" t="n">
-        <v>77.14380734735394</v>
+        <v>76.96242378253653</v>
       </c>
       <c r="O3" t="n">
-        <v>8.783154749140763</v>
+        <v>8.772823022410547</v>
       </c>
       <c r="P3" t="n">
-        <v>307.5059923493117</v>
+        <v>307.5089627921129</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19077,28 +19120,28 @@
         <v>0.1076</v>
       </c>
       <c r="I4" t="n">
-        <v>1.584955351015733</v>
+        <v>1.583780975466146</v>
       </c>
       <c r="J4" t="n">
+        <v>424</v>
+      </c>
+      <c r="K4" t="n">
         <v>423</v>
       </c>
-      <c r="K4" t="n">
-        <v>422</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6693409195960194</v>
+        <v>0.6700629944941096</v>
       </c>
       <c r="M4" t="n">
-        <v>6.82103707428189</v>
+        <v>6.813782765148718</v>
       </c>
       <c r="N4" t="n">
-        <v>72.68719376550882</v>
+        <v>72.53160898617777</v>
       </c>
       <c r="O4" t="n">
-        <v>8.525678492971032</v>
+        <v>8.516549124274325</v>
       </c>
       <c r="P4" t="n">
-        <v>309.3237795160349</v>
+        <v>309.3358180520711</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19155,28 +19198,28 @@
         <v>0.1482</v>
       </c>
       <c r="I5" t="n">
-        <v>1.186393813534313</v>
+        <v>1.185014109824217</v>
       </c>
       <c r="J5" t="n">
+        <v>424</v>
+      </c>
+      <c r="K5" t="n">
         <v>423</v>
       </c>
-      <c r="K5" t="n">
-        <v>422</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6812762428673442</v>
+        <v>0.6817235617363362</v>
       </c>
       <c r="M5" t="n">
-        <v>4.892260331166051</v>
+        <v>4.890824920095242</v>
       </c>
       <c r="N5" t="n">
-        <v>38.56911718165947</v>
+        <v>38.50036982422682</v>
       </c>
       <c r="O5" t="n">
-        <v>6.210403946738044</v>
+        <v>6.204866624209324</v>
       </c>
       <c r="P5" t="n">
-        <v>309.7924406096918</v>
+        <v>309.8065839668481</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19233,28 +19276,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1.029662255152925</v>
+        <v>1.028219217411513</v>
       </c>
       <c r="J6" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K6" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6655165767361969</v>
+        <v>0.6658272968456689</v>
       </c>
       <c r="M6" t="n">
-        <v>4.431633873465185</v>
+        <v>4.430740623467877</v>
       </c>
       <c r="N6" t="n">
-        <v>30.98034178884255</v>
+        <v>30.93121144501484</v>
       </c>
       <c r="O6" t="n">
-        <v>5.565998723395698</v>
+        <v>5.561583537538103</v>
       </c>
       <c r="P6" t="n">
-        <v>308.670226035386</v>
+        <v>308.685102631992</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19311,28 +19354,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7980204261434362</v>
+        <v>0.7982056032610276</v>
       </c>
       <c r="J7" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K7" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07145148362277642</v>
+        <v>0.07181183942326763</v>
       </c>
       <c r="M7" t="n">
-        <v>9.704945160339857</v>
+        <v>9.682102443007935</v>
       </c>
       <c r="N7" t="n">
-        <v>488.3005840157423</v>
+        <v>487.1493400050375</v>
       </c>
       <c r="O7" t="n">
-        <v>22.09752438658553</v>
+        <v>22.07145985214928</v>
       </c>
       <c r="P7" t="n">
-        <v>327.5080675338922</v>
+        <v>327.5061800025025</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19389,28 +19432,28 @@
         <v>0.0565</v>
       </c>
       <c r="I8" t="n">
-        <v>1.928612425569599</v>
+        <v>1.928030576484498</v>
       </c>
       <c r="J8" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K8" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6770474483702547</v>
+        <v>0.6779966798058386</v>
       </c>
       <c r="M8" t="n">
-        <v>8.024866339402374</v>
+        <v>8.010089484424014</v>
       </c>
       <c r="N8" t="n">
-        <v>103.1550354339014</v>
+        <v>102.9145401014588</v>
       </c>
       <c r="O8" t="n">
-        <v>10.15652674066786</v>
+        <v>10.14468038439156</v>
       </c>
       <c r="P8" t="n">
-        <v>316.4469723100707</v>
+        <v>316.4529707215302</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19448,7 +19491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I424"/>
+  <dimension ref="A1:I425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39343,6 +39386,53 @@
         </is>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>-42.477496360744524,173.53200312215637</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>-42.477884587274396,173.53126068827746</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>-42.478331878388964,173.53059757530096</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>-42.47874900574889,173.529878594562</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>-42.479285795075135,173.52931491720096</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>-42.47993422028019,173.52908426802202</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>-42.48060871473403,173.52916970742496</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0394/nzd0394.xlsx
+++ b/data/nzd0394/nzd0394.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I425"/>
+  <dimension ref="A1:I427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14447,6 +14447,72 @@
         <v>366.52</v>
       </c>
       <c r="I425" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>364.33</v>
+      </c>
+      <c r="C426" t="n">
+        <v>351.47</v>
+      </c>
+      <c r="D426" t="n">
+        <v>349.51</v>
+      </c>
+      <c r="E426" t="n">
+        <v>338.9</v>
+      </c>
+      <c r="F426" t="n">
+        <v>333.45</v>
+      </c>
+      <c r="G426" t="n">
+        <v>349.73</v>
+      </c>
+      <c r="H426" t="n">
+        <v>365.31</v>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>367.14</v>
+      </c>
+      <c r="C427" t="n">
+        <v>350.28</v>
+      </c>
+      <c r="D427" t="n">
+        <v>349.77</v>
+      </c>
+      <c r="E427" t="n">
+        <v>341.65</v>
+      </c>
+      <c r="F427" t="n">
+        <v>335.3</v>
+      </c>
+      <c r="G427" t="n">
+        <v>350.32</v>
+      </c>
+      <c r="H427" t="n">
+        <v>366.09</v>
+      </c>
+      <c r="I427" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14463,7 +14529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B433"/>
+  <dimension ref="A1:B435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18796,6 +18862,26 @@
       </c>
       <c r="B433" t="n">
         <v>-0.35</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -18964,28 +19050,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>1.351479149865364</v>
+        <v>1.353924445258486</v>
       </c>
       <c r="J2" t="n">
+        <v>426</v>
+      </c>
+      <c r="K2" t="n">
         <v>424</v>
       </c>
-      <c r="K2" t="n">
-        <v>422</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.5329518114025387</v>
+        <v>0.536208369791408</v>
       </c>
       <c r="M2" t="n">
-        <v>7.847760580978392</v>
+        <v>7.823141837902937</v>
       </c>
       <c r="N2" t="n">
-        <v>93.30578481504209</v>
+        <v>92.90954715787693</v>
       </c>
       <c r="O2" t="n">
-        <v>9.659491954292529</v>
+        <v>9.638959858712813</v>
       </c>
       <c r="P2" t="n">
-        <v>326.9070264252925</v>
+        <v>326.8817282273383</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19042,28 +19128,28 @@
         <v>0.1522</v>
       </c>
       <c r="I3" t="n">
-        <v>1.672688584890807</v>
+        <v>1.671541180121114</v>
       </c>
       <c r="J3" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="K3" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6810083505470863</v>
+        <v>0.6828339288878216</v>
       </c>
       <c r="M3" t="n">
-        <v>7.281433260599537</v>
+        <v>7.255324012425183</v>
       </c>
       <c r="N3" t="n">
-        <v>76.96242378253653</v>
+        <v>76.60989972565544</v>
       </c>
       <c r="O3" t="n">
-        <v>8.772823022410547</v>
+        <v>8.752708136665785</v>
       </c>
       <c r="P3" t="n">
-        <v>307.5089627921129</v>
+        <v>307.5207665189047</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19120,28 +19206,28 @@
         <v>0.1076</v>
       </c>
       <c r="I4" t="n">
-        <v>1.583780975466146</v>
+        <v>1.582029629881095</v>
       </c>
       <c r="J4" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="K4" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6700629944941096</v>
+        <v>0.6717078871271733</v>
       </c>
       <c r="M4" t="n">
-        <v>6.813782765148718</v>
+        <v>6.794820788386668</v>
       </c>
       <c r="N4" t="n">
-        <v>72.53160898617777</v>
+        <v>72.20850121535484</v>
       </c>
       <c r="O4" t="n">
-        <v>8.516549124274325</v>
+        <v>8.497558544391138</v>
       </c>
       <c r="P4" t="n">
-        <v>309.3358180520711</v>
+        <v>309.3538248983688</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19198,28 +19284,28 @@
         <v>0.1482</v>
       </c>
       <c r="I5" t="n">
-        <v>1.185014109824217</v>
+        <v>1.183980571415672</v>
       </c>
       <c r="J5" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="K5" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6817235617363362</v>
+        <v>0.6834092647889534</v>
       </c>
       <c r="M5" t="n">
-        <v>4.890824920095242</v>
+        <v>4.876276852194941</v>
       </c>
       <c r="N5" t="n">
-        <v>38.50036982422682</v>
+        <v>38.33412848758061</v>
       </c>
       <c r="O5" t="n">
-        <v>6.204866624209324</v>
+        <v>6.191456087834315</v>
       </c>
       <c r="P5" t="n">
-        <v>309.8065839668481</v>
+        <v>309.8171985036898</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19276,28 +19362,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1.028219217411513</v>
+        <v>1.026648239445875</v>
       </c>
       <c r="J6" t="n">
+        <v>426</v>
+      </c>
+      <c r="K6" t="n">
         <v>424</v>
       </c>
-      <c r="K6" t="n">
-        <v>422</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.6658272968456689</v>
+        <v>0.6672259219156111</v>
       </c>
       <c r="M6" t="n">
-        <v>4.430740623467877</v>
+        <v>4.42020555392494</v>
       </c>
       <c r="N6" t="n">
-        <v>30.93121144501484</v>
+        <v>30.80364275511842</v>
       </c>
       <c r="O6" t="n">
-        <v>5.561583537538103</v>
+        <v>5.550102949956732</v>
       </c>
       <c r="P6" t="n">
-        <v>308.685102631992</v>
+        <v>308.7013387740174</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19354,28 +19440,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7982056032610276</v>
+        <v>0.7992690537748313</v>
       </c>
       <c r="J7" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="K7" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07181183942326763</v>
+        <v>0.07265169733337284</v>
       </c>
       <c r="M7" t="n">
-        <v>9.682102443007935</v>
+        <v>9.636874581936786</v>
       </c>
       <c r="N7" t="n">
-        <v>487.1493400050375</v>
+        <v>484.8693870179765</v>
       </c>
       <c r="O7" t="n">
-        <v>22.07145985214928</v>
+        <v>22.01974993086834</v>
       </c>
       <c r="P7" t="n">
-        <v>327.5061800025025</v>
+        <v>327.4953043186736</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19432,28 +19518,28 @@
         <v>0.0565</v>
       </c>
       <c r="I8" t="n">
-        <v>1.928030576484498</v>
+        <v>1.926046010596769</v>
       </c>
       <c r="J8" t="n">
+        <v>426</v>
+      </c>
+      <c r="K8" t="n">
         <v>424</v>
       </c>
-      <c r="K8" t="n">
-        <v>422</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.6779966798058386</v>
+        <v>0.6796656528781636</v>
       </c>
       <c r="M8" t="n">
-        <v>8.010089484424014</v>
+        <v>7.986639143579277</v>
       </c>
       <c r="N8" t="n">
-        <v>102.9145401014588</v>
+        <v>102.4527606898717</v>
       </c>
       <c r="O8" t="n">
-        <v>10.14468038439156</v>
+        <v>10.12189511355812</v>
       </c>
       <c r="P8" t="n">
-        <v>316.4529707215302</v>
+        <v>316.4734887294059</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19491,7 +19577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I425"/>
+  <dimension ref="A1:I427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39433,6 +39519,100 @@
         </is>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>-42.47750378973531,173.53201304387</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>-42.47788497153494,173.53126120146945</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>-42.47833565620212,173.53060279430994</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>-42.47875235734964,173.52988432029082</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>-42.479288372317846,173.52932091453607</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>-42.479935684300074,173.52909066050648</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>-42.48060726257582,173.52915511735887</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>-42.4775217858214,173.53203707837568</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>-42.47787735036727,173.53125102316267</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>-42.478337293254405,173.5306050558807</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>-42.478767718849404,173.52991056322236</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>-42.4792967370507,173.5293403795744</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>-42.47993725479377,173.52909751789926</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>-42.48060819867802,173.52916452252535</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0394/nzd0394.xlsx
+++ b/data/nzd0394/nzd0394.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I427"/>
+  <dimension ref="A1:I430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14513,6 +14513,105 @@
         <v>366.09</v>
       </c>
       <c r="I427" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:02+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>366.1</v>
+      </c>
+      <c r="C428" t="n">
+        <v>348.62</v>
+      </c>
+      <c r="D428" t="n">
+        <v>348.85</v>
+      </c>
+      <c r="E428" t="n">
+        <v>341.43</v>
+      </c>
+      <c r="F428" t="n">
+        <v>334.49</v>
+      </c>
+      <c r="G428" t="n">
+        <v>348.65</v>
+      </c>
+      <c r="H428" t="n">
+        <v>365</v>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>366.1</v>
+      </c>
+      <c r="C429" t="n">
+        <v>347.99</v>
+      </c>
+      <c r="D429" t="n">
+        <v>348.29</v>
+      </c>
+      <c r="E429" t="n">
+        <v>341.32</v>
+      </c>
+      <c r="F429" t="n">
+        <v>335.31</v>
+      </c>
+      <c r="G429" t="n">
+        <v>349.54</v>
+      </c>
+      <c r="H429" t="n">
+        <v>364.92</v>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>365.65</v>
+      </c>
+      <c r="C430" t="n">
+        <v>347.96</v>
+      </c>
+      <c r="D430" t="n">
+        <v>348.76</v>
+      </c>
+      <c r="E430" t="n">
+        <v>341.66</v>
+      </c>
+      <c r="F430" t="n">
+        <v>335.4</v>
+      </c>
+      <c r="G430" t="n">
+        <v>349.58</v>
+      </c>
+      <c r="H430" t="n">
+        <v>365.28</v>
+      </c>
+      <c r="I430" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14529,7 +14628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B435"/>
+  <dimension ref="A1:B438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18882,6 +18981,36 @@
       </c>
       <c r="B435" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -19050,28 +19179,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>1.353924445258486</v>
+        <v>1.357612957671597</v>
       </c>
       <c r="J2" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K2" t="n">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="L2" t="n">
-        <v>0.536208369791408</v>
+        <v>0.5410907500973146</v>
       </c>
       <c r="M2" t="n">
-        <v>7.823141837902937</v>
+        <v>7.786640566385627</v>
       </c>
       <c r="N2" t="n">
-        <v>92.90954715787693</v>
+        <v>92.31109950534666</v>
       </c>
       <c r="O2" t="n">
-        <v>9.638959858712813</v>
+        <v>9.607866542856778</v>
       </c>
       <c r="P2" t="n">
-        <v>326.8817282273383</v>
+        <v>326.8434363327581</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19128,28 +19257,28 @@
         <v>0.1522</v>
       </c>
       <c r="I3" t="n">
-        <v>1.671541180121114</v>
+        <v>1.66616764105682</v>
       </c>
       <c r="J3" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K3" t="n">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6828339288878216</v>
+        <v>0.6843005274504602</v>
       </c>
       <c r="M3" t="n">
-        <v>7.255324012425183</v>
+        <v>7.242402513588272</v>
       </c>
       <c r="N3" t="n">
-        <v>76.60989972565544</v>
+        <v>76.1892739006116</v>
       </c>
       <c r="O3" t="n">
-        <v>8.752708136665785</v>
+        <v>8.728646739364104</v>
       </c>
       <c r="P3" t="n">
-        <v>307.5207665189047</v>
+        <v>307.5762457213943</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19206,28 +19335,28 @@
         <v>0.1076</v>
       </c>
       <c r="I4" t="n">
-        <v>1.582029629881095</v>
+        <v>1.577972838909985</v>
       </c>
       <c r="J4" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K4" t="n">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6717078871271733</v>
+        <v>0.6736210353223469</v>
       </c>
       <c r="M4" t="n">
-        <v>6.794820788386668</v>
+        <v>6.777224501068801</v>
       </c>
       <c r="N4" t="n">
-        <v>72.20850121535484</v>
+        <v>71.76869160363592</v>
       </c>
       <c r="O4" t="n">
-        <v>8.497558544391138</v>
+        <v>8.471640431677676</v>
       </c>
       <c r="P4" t="n">
-        <v>309.3538248983688</v>
+        <v>309.3957074873507</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19284,28 +19413,28 @@
         <v>0.1482</v>
       </c>
       <c r="I5" t="n">
-        <v>1.183980571415672</v>
+        <v>1.183895214549207</v>
       </c>
       <c r="J5" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K5" t="n">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6834092647889534</v>
+        <v>0.6865597426579453</v>
       </c>
       <c r="M5" t="n">
-        <v>4.876276852194941</v>
+        <v>4.843194034604071</v>
       </c>
       <c r="N5" t="n">
-        <v>38.33412848758061</v>
+        <v>38.06557835630024</v>
       </c>
       <c r="O5" t="n">
-        <v>6.191456087834315</v>
+        <v>6.169730817167006</v>
       </c>
       <c r="P5" t="n">
-        <v>309.8171985036898</v>
+        <v>309.8180788847746</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19362,28 +19491,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1.026648239445875</v>
+        <v>1.025153068338778</v>
       </c>
       <c r="J6" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K6" t="n">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6672259219156111</v>
+        <v>0.6697865188013101</v>
       </c>
       <c r="M6" t="n">
-        <v>4.42020555392494</v>
+        <v>4.398870629673221</v>
       </c>
       <c r="N6" t="n">
-        <v>30.80364275511842</v>
+        <v>30.59715895204557</v>
       </c>
       <c r="O6" t="n">
-        <v>5.550102949956732</v>
+        <v>5.531469872650991</v>
       </c>
       <c r="P6" t="n">
-        <v>308.7013387740174</v>
+        <v>308.7168577295539</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19440,28 +19569,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7992690537748313</v>
+        <v>0.7997238168791252</v>
       </c>
       <c r="J7" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K7" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07265169733337284</v>
+        <v>0.07372593047538611</v>
       </c>
       <c r="M7" t="n">
-        <v>9.636874581936786</v>
+        <v>9.570708366492688</v>
       </c>
       <c r="N7" t="n">
-        <v>484.8693870179765</v>
+        <v>481.4807362798853</v>
       </c>
       <c r="O7" t="n">
-        <v>22.01974993086834</v>
+        <v>21.94266930616887</v>
       </c>
       <c r="P7" t="n">
-        <v>327.4953043186736</v>
+        <v>327.490631610151</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19518,28 +19647,28 @@
         <v>0.0565</v>
       </c>
       <c r="I8" t="n">
-        <v>1.926046010596769</v>
+        <v>1.922093015230614</v>
       </c>
       <c r="J8" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K8" t="n">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6796656528781636</v>
+        <v>0.6818553749596075</v>
       </c>
       <c r="M8" t="n">
-        <v>7.986639143579277</v>
+        <v>7.958897185730868</v>
       </c>
       <c r="N8" t="n">
-        <v>102.4527606898717</v>
+        <v>101.7949881715127</v>
       </c>
       <c r="O8" t="n">
-        <v>10.12189511355812</v>
+        <v>10.0893502353478</v>
       </c>
       <c r="P8" t="n">
-        <v>316.4734887294059</v>
+        <v>316.5145279684351</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19577,7 +19706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I427"/>
+  <dimension ref="A1:I430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39613,6 +39742,147 @@
         </is>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:02+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>-42.477515125348866,173.53202818304104</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>-42.47786671915705,173.5312368248565</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>-42.47833150060764,173.5305970534001</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>-42.47876648992965,173.52990846378736</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>-42.47929307465456,173.52933185704345</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>-42.47993280949704,173.5290781079918</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>-42.480606890535,173.52915137940815</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>-42.477515125348866,173.53202818304104</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>-42.47786268442016,173.53123143634397</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>-42.47832797464845,173.53059218232565</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>-42.478765875469755,173.5299074140699</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>-42.479296782265465,173.52934048479085</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>-42.47993517854781,173.52908845219363</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>-42.480606794524434,173.52915041477573</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>-42.4775122434134,173.5320243340987</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>-42.47786249228983,173.53123117974815</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>-42.478330933935645,173.5305962705488</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-42.4787677747094,173.5299106586512</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>-42.479297189198334,173.52934143173877</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>-42.479935285021966,173.5290889171016</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>-42.48060722657188,173.5291547556217</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0394/nzd0394.xlsx
+++ b/data/nzd0394/nzd0394.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I430"/>
+  <dimension ref="A1:I432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14612,6 +14612,72 @@
         <v>365.28</v>
       </c>
       <c r="I430" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>362.93</v>
+      </c>
+      <c r="C431" t="n">
+        <v>347.27</v>
+      </c>
+      <c r="D431" t="n">
+        <v>347.91</v>
+      </c>
+      <c r="E431" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="F431" t="n">
+        <v>334.87</v>
+      </c>
+      <c r="G431" t="n">
+        <v>349.17</v>
+      </c>
+      <c r="H431" t="n">
+        <v>364.46</v>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>363.02</v>
+      </c>
+      <c r="C432" t="n">
+        <v>346.34</v>
+      </c>
+      <c r="D432" t="n">
+        <v>347.92</v>
+      </c>
+      <c r="E432" t="n">
+        <v>341.94</v>
+      </c>
+      <c r="F432" t="n">
+        <v>335.79</v>
+      </c>
+      <c r="G432" t="n">
+        <v>349.85</v>
+      </c>
+      <c r="H432" t="n">
+        <v>364.06</v>
+      </c>
+      <c r="I432" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14628,7 +14694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B438"/>
+  <dimension ref="A1:B440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19011,6 +19077,26 @@
       </c>
       <c r="B438" t="n">
         <v>0.6</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -19179,28 +19265,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>1.357612957671597</v>
+        <v>1.357340533756447</v>
       </c>
       <c r="J2" t="n">
+        <v>431</v>
+      </c>
+      <c r="K2" t="n">
         <v>429</v>
       </c>
-      <c r="K2" t="n">
-        <v>427</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.5410907500973146</v>
+        <v>0.5434037146239494</v>
       </c>
       <c r="M2" t="n">
-        <v>7.786640566385627</v>
+        <v>7.751867333284305</v>
       </c>
       <c r="N2" t="n">
-        <v>92.31109950534666</v>
+        <v>91.88119996151934</v>
       </c>
       <c r="O2" t="n">
-        <v>9.607866542856778</v>
+        <v>9.585468166006256</v>
       </c>
       <c r="P2" t="n">
-        <v>326.8434363327581</v>
+        <v>326.8462716591862</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19257,28 +19343,28 @@
         <v>0.1522</v>
       </c>
       <c r="I3" t="n">
-        <v>1.66616764105682</v>
+        <v>1.6614178728287</v>
       </c>
       <c r="J3" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K3" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6843005274504602</v>
+        <v>0.6847641884396948</v>
       </c>
       <c r="M3" t="n">
-        <v>7.242402513588272</v>
+        <v>7.242065401107984</v>
       </c>
       <c r="N3" t="n">
-        <v>76.1892739006116</v>
+        <v>75.9744340391226</v>
       </c>
       <c r="O3" t="n">
-        <v>8.728646739364104</v>
+        <v>8.716331455326984</v>
       </c>
       <c r="P3" t="n">
-        <v>307.5762457213943</v>
+        <v>307.6254087922344</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19335,28 +19421,28 @@
         <v>0.1076</v>
       </c>
       <c r="I4" t="n">
-        <v>1.577972838909985</v>
+        <v>1.57465684026998</v>
       </c>
       <c r="J4" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K4" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6736210353223469</v>
+        <v>0.6746191305462576</v>
       </c>
       <c r="M4" t="n">
-        <v>6.777224501068801</v>
+        <v>6.770067198284323</v>
       </c>
       <c r="N4" t="n">
-        <v>71.76869160363592</v>
+        <v>71.50236709085787</v>
       </c>
       <c r="O4" t="n">
-        <v>8.471640431677676</v>
+        <v>8.45590723050211</v>
       </c>
       <c r="P4" t="n">
-        <v>309.3957074873507</v>
+        <v>309.4300286481164</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19413,28 +19499,28 @@
         <v>0.1482</v>
       </c>
       <c r="I5" t="n">
-        <v>1.183895214549207</v>
+        <v>1.183832410741854</v>
       </c>
       <c r="J5" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K5" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6865597426579453</v>
+        <v>0.6886150049234196</v>
       </c>
       <c r="M5" t="n">
-        <v>4.843194034604071</v>
+        <v>4.822684772260728</v>
       </c>
       <c r="N5" t="n">
-        <v>38.06557835630024</v>
+        <v>37.88932422395008</v>
       </c>
       <c r="O5" t="n">
-        <v>6.169730817167006</v>
+        <v>6.155430466177819</v>
       </c>
       <c r="P5" t="n">
-        <v>309.8180788847746</v>
+        <v>309.8187270479272</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19491,28 +19577,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1.025153068338778</v>
+        <v>1.024366773630062</v>
       </c>
       <c r="J6" t="n">
+        <v>431</v>
+      </c>
+      <c r="K6" t="n">
         <v>429</v>
       </c>
-      <c r="K6" t="n">
-        <v>427</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.6697865188013101</v>
+        <v>0.671561481479209</v>
       </c>
       <c r="M6" t="n">
-        <v>4.398870629673221</v>
+        <v>4.383427863040012</v>
       </c>
       <c r="N6" t="n">
-        <v>30.59715895204557</v>
+        <v>30.45920212520392</v>
       </c>
       <c r="O6" t="n">
-        <v>5.531469872650991</v>
+        <v>5.518985606540745</v>
       </c>
       <c r="P6" t="n">
-        <v>308.7168577295539</v>
+        <v>308.7250396577099</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19569,28 +19655,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7997238168791252</v>
+        <v>0.8001997404638105</v>
       </c>
       <c r="J7" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K7" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07372593047538611</v>
+        <v>0.07447042011331484</v>
       </c>
       <c r="M7" t="n">
-        <v>9.570708366492688</v>
+        <v>9.526400885263358</v>
       </c>
       <c r="N7" t="n">
-        <v>481.4807362798853</v>
+        <v>479.2483942497516</v>
       </c>
       <c r="O7" t="n">
-        <v>21.94266930616887</v>
+        <v>21.89174260422755</v>
       </c>
       <c r="P7" t="n">
-        <v>327.490631610151</v>
+        <v>327.4857317441988</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19647,28 +19733,28 @@
         <v>0.0565</v>
       </c>
       <c r="I8" t="n">
-        <v>1.922093015230614</v>
+        <v>1.918745592046182</v>
       </c>
       <c r="J8" t="n">
+        <v>431</v>
+      </c>
+      <c r="K8" t="n">
         <v>429</v>
       </c>
-      <c r="K8" t="n">
-        <v>427</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.6818553749596075</v>
+        <v>0.6830613429418592</v>
       </c>
       <c r="M8" t="n">
-        <v>7.958897185730868</v>
+        <v>7.945805594581747</v>
       </c>
       <c r="N8" t="n">
-        <v>101.7949881715127</v>
+        <v>101.3886980745725</v>
       </c>
       <c r="O8" t="n">
-        <v>10.0893502353478</v>
+        <v>10.0691955028479</v>
       </c>
       <c r="P8" t="n">
-        <v>316.5145279684351</v>
+        <v>316.5493699532618</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19706,7 +19792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I430"/>
+  <dimension ref="A1:I432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39883,6 +39969,100 @@
         </is>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>-42.477494823711844,173.53200106938831</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>-42.477858073291976,173.5312252780448</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>-42.47832558203316,173.53058887695403</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>-42.47876464654995,173.52990531463502</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>-42.4792947928158,173.52933585526773</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>-42.47993419366164,173.52908415179505</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>-42.48060624246359,173.5291448681393</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>-42.4774954000991,173.53200183917633</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>-42.477852117250904,173.53121732357633</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>-42.47832564499672,173.53058896393748</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>-42.47876933878901,173.5299133306595</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>-42.47929895257399,173.52934553518</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>-42.479936003722564,173.52909205523042</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>-42.480605762410434,173.52914004497725</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0394/nzd0394.xlsx
+++ b/data/nzd0394/nzd0394.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I432"/>
+  <dimension ref="A1:I433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14678,6 +14678,39 @@
         <v>364.06</v>
       </c>
       <c r="I432" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>360.43</v>
+      </c>
+      <c r="C433" t="n">
+        <v>346.23</v>
+      </c>
+      <c r="D433" t="n">
+        <v>347.59</v>
+      </c>
+      <c r="E433" t="n">
+        <v>341.52</v>
+      </c>
+      <c r="F433" t="n">
+        <v>335.51</v>
+      </c>
+      <c r="G433" t="n">
+        <v>348.68</v>
+      </c>
+      <c r="H433" t="n">
+        <v>360.42</v>
+      </c>
+      <c r="I433" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14694,7 +14727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B440"/>
+  <dimension ref="A1:B441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19097,6 +19130,16 @@
       </c>
       <c r="B440" t="n">
         <v>0.34</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
@@ -19265,28 +19308,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>1.357340533756447</v>
+        <v>1.356042931693734</v>
       </c>
       <c r="J2" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K2" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5434037146239494</v>
+        <v>0.5440841380566452</v>
       </c>
       <c r="M2" t="n">
-        <v>7.751867333284305</v>
+        <v>7.741035158688769</v>
       </c>
       <c r="N2" t="n">
-        <v>91.88119996151934</v>
+        <v>91.68800780735275</v>
       </c>
       <c r="O2" t="n">
-        <v>9.585468166006256</v>
+        <v>9.575385517427105</v>
       </c>
       <c r="P2" t="n">
-        <v>326.8462716591862</v>
+        <v>326.8598388352625</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19343,28 +19386,28 @@
         <v>0.1522</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6614178728287</v>
+        <v>1.658755062620589</v>
       </c>
       <c r="J3" t="n">
+        <v>432</v>
+      </c>
+      <c r="K3" t="n">
         <v>431</v>
       </c>
-      <c r="K3" t="n">
-        <v>430</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.6847641884396948</v>
+        <v>0.684873531798285</v>
       </c>
       <c r="M3" t="n">
-        <v>7.242065401107984</v>
+        <v>7.243767841679451</v>
       </c>
       <c r="N3" t="n">
-        <v>75.9744340391226</v>
+        <v>75.88532638654335</v>
       </c>
       <c r="O3" t="n">
-        <v>8.716331455326984</v>
+        <v>8.711218421469143</v>
       </c>
       <c r="P3" t="n">
-        <v>307.6254087922344</v>
+        <v>307.6530952925246</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19421,28 +19464,28 @@
         <v>0.1076</v>
       </c>
       <c r="I4" t="n">
-        <v>1.57465684026998</v>
+        <v>1.572812882173112</v>
       </c>
       <c r="J4" t="n">
+        <v>432</v>
+      </c>
+      <c r="K4" t="n">
         <v>431</v>
       </c>
-      <c r="K4" t="n">
-        <v>430</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6746191305462576</v>
+        <v>0.6750436825202473</v>
       </c>
       <c r="M4" t="n">
-        <v>6.770067198284323</v>
+        <v>6.767773431300207</v>
       </c>
       <c r="N4" t="n">
-        <v>71.50236709085787</v>
+        <v>71.37826815078107</v>
       </c>
       <c r="O4" t="n">
-        <v>8.45590723050211</v>
+        <v>8.448566041097214</v>
       </c>
       <c r="P4" t="n">
-        <v>309.4300286481164</v>
+        <v>309.4492011547519</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19499,28 +19542,28 @@
         <v>0.1482</v>
       </c>
       <c r="I5" t="n">
-        <v>1.183832410741854</v>
+        <v>1.183751349081405</v>
       </c>
       <c r="J5" t="n">
+        <v>432</v>
+      </c>
+      <c r="K5" t="n">
         <v>431</v>
       </c>
-      <c r="K5" t="n">
-        <v>430</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6886150049234196</v>
+        <v>0.6896272279448465</v>
       </c>
       <c r="M5" t="n">
-        <v>4.822684772260728</v>
+        <v>4.812085360332468</v>
       </c>
       <c r="N5" t="n">
-        <v>37.88932422395008</v>
+        <v>37.80149473883527</v>
       </c>
       <c r="O5" t="n">
-        <v>6.155430466177819</v>
+        <v>6.148292018018929</v>
       </c>
       <c r="P5" t="n">
-        <v>309.8187270479272</v>
+        <v>309.8195698844459</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19577,28 +19620,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1.024366773630062</v>
+        <v>1.024011125806215</v>
       </c>
       <c r="J6" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K6" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L6" t="n">
-        <v>0.671561481479209</v>
+        <v>0.6724726323979203</v>
       </c>
       <c r="M6" t="n">
-        <v>4.383427863040012</v>
+        <v>4.375499471899432</v>
       </c>
       <c r="N6" t="n">
-        <v>30.45920212520392</v>
+        <v>30.38990561470367</v>
       </c>
       <c r="O6" t="n">
-        <v>5.518985606540745</v>
+        <v>5.512704020233961</v>
       </c>
       <c r="P6" t="n">
-        <v>308.7250396577099</v>
+        <v>308.7287581603125</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19655,28 +19698,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8001997404638105</v>
+        <v>0.8000419529777772</v>
       </c>
       <c r="J7" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K7" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07447042011331484</v>
+        <v>0.07477800109110544</v>
       </c>
       <c r="M7" t="n">
-        <v>9.526400885263358</v>
+        <v>9.506007704876181</v>
       </c>
       <c r="N7" t="n">
-        <v>479.2483942497516</v>
+        <v>478.1393321958899</v>
       </c>
       <c r="O7" t="n">
-        <v>21.89174260422755</v>
+        <v>21.86639733005622</v>
       </c>
       <c r="P7" t="n">
-        <v>327.4857317441988</v>
+        <v>327.4873632165166</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19733,28 +19776,28 @@
         <v>0.0565</v>
       </c>
       <c r="I8" t="n">
-        <v>1.918745592046182</v>
+        <v>1.915336441491705</v>
       </c>
       <c r="J8" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K8" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6830613429418592</v>
+        <v>0.6830452026855587</v>
       </c>
       <c r="M8" t="n">
-        <v>7.945805594581747</v>
+        <v>7.951753883073239</v>
       </c>
       <c r="N8" t="n">
-        <v>101.3886980745725</v>
+        <v>101.2943094386837</v>
       </c>
       <c r="O8" t="n">
-        <v>10.0691955028479</v>
+        <v>10.06450741162645</v>
       </c>
       <c r="P8" t="n">
-        <v>316.5493699532618</v>
+        <v>316.5850145835935</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19792,7 +19835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I432"/>
+  <dimension ref="A1:I433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40063,6 +40106,53 @@
         </is>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>-42.477478812952455,173.53197968639387</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>-42.47785141277289,173.53121638272532</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>-42.47832356719917,173.53058609348338</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-42.47876699266955,173.52990932264711</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>-42.47929768656071,173.5293425891196</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>-42.47993288935271,173.52907845667272</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>-42.48060139391754,173.529096154206</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
